--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42182</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41818</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41454</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41090</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4655600</v>
+      </c>
+      <c r="E8" s="3">
         <v>4451600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4138700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4088200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3869900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4731700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4946200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5280600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2632200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4603900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4060800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3539800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3173200</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2975200</v>
+      </c>
+      <c r="E9" s="3">
         <v>2996200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2722500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2593300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2436200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2900200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2966700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3228800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1553300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2891400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2613100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2259800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2077700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1680400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1455400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1416200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1494900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1433700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1831500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1979500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2051800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1078900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1712500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1447700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1280000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1095600</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,50 +875,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E12" s="3">
         <v>123100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>122000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>121700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>119200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>218600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>167700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>184000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>88200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>187800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>152500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>115200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>105800</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -946,51 +962,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E14" s="3">
         <v>96100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>230800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>55500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>245900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>243700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2663100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>243400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>218800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8800</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1030,9 +1052,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4500500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4381600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3728300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3843000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3695400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4495700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4483200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7281400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2565500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3866700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3659600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2860700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2604000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>155100</v>
+      </c>
+      <c r="E18" s="3">
         <v>70000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>410400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>245200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>174500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>236000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>463000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2000800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>66700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>737200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>401200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>679100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>569200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1148,97 +1180,104 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-209100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-151700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-239300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-26500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>54600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-182900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2847500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>31100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-342100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-23000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>351800</v>
+      </c>
+      <c r="E21" s="3">
         <v>199500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>570900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>390700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>544500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>714200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>724900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4391300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>280200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>943900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>737100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>837900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>712000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>17</v>
+      <c r="D22" s="3">
+        <v>600</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -1258,108 +1297,117 @@
       <c r="J22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="3">
         <v>88900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>147100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>105600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>64700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-139100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>258700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>148000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>290600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>280100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4848300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>248000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>272600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>607700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>512000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-8200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>389600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-38300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>159600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>145400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-835500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-33600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>120000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>67300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>165800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>119000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-130900</v>
+        <v>-4400</v>
       </c>
       <c r="E26" s="3">
         <v>-130900</v>
       </c>
       <c r="F26" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="G26" s="3">
         <v>44200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>158700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>131000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>134700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4012800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>42500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>128000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>205300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>441900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>393000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-130900</v>
+        <v>-4400</v>
       </c>
       <c r="E27" s="3">
         <v>-130900</v>
       </c>
       <c r="F27" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="G27" s="3">
         <v>44200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>158700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>131000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>134700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4012800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>42500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>128000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>205300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>441900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>393000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,32 +1582,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E29" s="3">
         <v>-9700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>62000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-206800</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-12600</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-15100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1558,18 +1618,21 @@
       <c r="L29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>8600</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E32" s="3">
         <v>209100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>151700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>239300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>26500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-54600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>182900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2847500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-31100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>342100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>23000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-140600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-68900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-162600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>131000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>119600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4012800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>42500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>128000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>205300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>441900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>401600</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-140600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-68900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-162600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>131000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>119600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4012800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>42500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>128000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>205300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>441900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>401600</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42182</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41818</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41454</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41090</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>751300</v>
+      </c>
+      <c r="E41" s="3">
         <v>600700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1864900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>641500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>354300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>551100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>678700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>622300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>417800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>785600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>799500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1559800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>602500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1954,16 +2043,16 @@
         <v>100</v>
       </c>
       <c r="E42" s="3">
+        <v>100</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6600</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>17</v>
@@ -1971,209 +2060,224 @@
       <c r="J42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42" s="3">
         <v>14900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>800</v>
       </c>
-      <c r="O42" s="3" t="s">
+      <c r="P42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>768100</v>
+      </c>
+      <c r="E43" s="3">
         <v>738600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>693100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1073900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1269500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1073100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1130800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1176000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2710900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1282100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>935100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1316000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>573600</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1140900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1150300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1020200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1200200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>967300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>878000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>806900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>795000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>898700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>838900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>631600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1407800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>547500</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E45" s="3">
         <v>230200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>281300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>215400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>159200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>203200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>212000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>286100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>263600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>178800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>195500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72300</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2832900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2719900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3859900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3133500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2756900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2902200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2819600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2805300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2791600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3182900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2550900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2236900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1795900</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>65100</v>
+        <v>60100</v>
       </c>
       <c r="E47" s="3">
-        <v>68200</v>
+        <v>63400</v>
       </c>
       <c r="F47" s="3">
+        <v>66400</v>
+      </c>
+      <c r="G47" s="3">
         <v>71700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20100</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>17</v>
@@ -2181,108 +2285,117 @@
       <c r="J47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="3">
         <v>220500</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O47" s="3">
         <v>4400</v>
       </c>
-      <c r="O47" s="3" t="s">
+      <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1113700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1165400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1058900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1213000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1060300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>829100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>833100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>870100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1772400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>932400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>779900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2653200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>578400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6515200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6779200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5150800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6758200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7106700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>6888000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7556200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9910700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15352100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15340600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10330800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4663400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1549400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>287700</v>
+        <v>287200</v>
       </c>
       <c r="E52" s="3">
-        <v>287900</v>
+        <v>289400</v>
       </c>
       <c r="F52" s="3">
+        <v>289700</v>
+      </c>
+      <c r="G52" s="3">
         <v>312000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>357400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>364100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>419900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>284000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>336200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>264700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>191200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>201600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10809100</v>
+      </c>
+      <c r="E54" s="3">
         <v>11017300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10425700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11488400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11301400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10983400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11628800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13870100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19349600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19720600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13852800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5350800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4024000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>477700</v>
+      </c>
+      <c r="E57" s="3">
         <v>537300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>411200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>543800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>520200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>474900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>450200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>471700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1468900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>747500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>364300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>764000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>317300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>440600</v>
+      </c>
+      <c r="E58" s="3">
         <v>36200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>603800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>37800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>190200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>70400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>572800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7050400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>64600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>143700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>92400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>40100</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>668000</v>
+      </c>
+      <c r="E59" s="3">
         <v>540100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>572900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>800400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>812200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>872300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>915400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>791800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1172600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>881600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>566700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>642400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>295300</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1586300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1113600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1587900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1382000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1335800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1537400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1436000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1836300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2552200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1693700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1074700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>749400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>652700</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3632800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4070400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2916700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3528300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3365800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3052200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3270800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5224500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4971600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5246900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3063100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1927800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1329200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>822100</v>
+      </c>
+      <c r="E62" s="3">
         <v>991200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>769400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>923000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>795700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>725700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>751400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>851700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3341800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2117200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1021300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>682000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>189400</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6041200</v>
+      </c>
+      <c r="E66" s="3">
         <v>6175200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5274000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5833300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5497600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5315400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5458300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7912000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9242200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9058000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5159900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3019400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2173000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2080300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2067600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1927000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1858100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1695500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1838300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1975500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2095100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3462100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1938300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1875100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3431800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1306900</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4767900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4842100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5151700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5655100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5803800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5668000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6170500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5958100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10107400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10662600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8692900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2331400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1851000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42182</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41818</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41454</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41090</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-140600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-68900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-162600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>131000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>119600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4012800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>42500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>128000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>205300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>441900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>401600</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>359500</v>
+      </c>
+      <c r="E83" s="3">
         <v>338600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>312200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>384800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>396500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>423600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>444800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>457000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>182400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>548800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>358900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>160200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>135300</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>405500</v>
+      </c>
+      <c r="E89" s="3">
         <v>307300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>156300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>636200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>387800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>593000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>698900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>654900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>200900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1198300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>693500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>553800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>513400</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-101700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-96400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-222700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-205600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-286800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-138200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-88600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-171300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-77800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-137000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-171600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-104100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-120900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-77500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1958600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1275800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-187800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-596100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-126800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2338100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-175000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-708100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2646900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1704800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-947800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-684100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-149700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-142400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-129600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-123900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-112400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-104900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-91100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-83200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-36300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-64800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-46100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-33000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-29000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-187200</v>
+      </c>
+      <c r="E100" s="3">
         <v>421600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-178700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-181100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-571900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3004700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-268700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>149600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1523900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1028000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>577200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>458700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-48900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-15600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>19900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-21900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-10200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-89200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4400</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1278600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1237800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>287200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-196800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-127600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>56400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>204500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-367800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>177400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>292400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -990,7 +990,7 @@
         <v>245900</v>
       </c>
       <c r="J14" s="3">
-        <v>243700</v>
+        <v>244700</v>
       </c>
       <c r="K14" s="3">
         <v>2663100</v>
@@ -1096,7 +1096,7 @@
         <v>4495700</v>
       </c>
       <c r="J17" s="3">
-        <v>4483200</v>
+        <v>4484200</v>
       </c>
       <c r="K17" s="3">
         <v>7281400</v>
@@ -1141,7 +1141,7 @@
         <v>236000</v>
       </c>
       <c r="J18" s="3">
-        <v>463000</v>
+        <v>462000</v>
       </c>
       <c r="K18" s="3">
         <v>-2000800</v>
@@ -1250,7 +1250,7 @@
         <v>714200</v>
       </c>
       <c r="J21" s="3">
-        <v>724900</v>
+        <v>723900</v>
       </c>
       <c r="K21" s="3">
         <v>-4391300</v>
@@ -1340,7 +1340,7 @@
         <v>290600</v>
       </c>
       <c r="J23" s="3">
-        <v>280100</v>
+        <v>279100</v>
       </c>
       <c r="K23" s="3">
         <v>-4848300</v>
@@ -1475,7 +1475,7 @@
         <v>131000</v>
       </c>
       <c r="J26" s="3">
-        <v>134700</v>
+        <v>133700</v>
       </c>
       <c r="K26" s="3">
         <v>-4012800</v>
@@ -1520,7 +1520,7 @@
         <v>131000</v>
       </c>
       <c r="J27" s="3">
-        <v>134700</v>
+        <v>133700</v>
       </c>
       <c r="K27" s="3">
         <v>-4012800</v>
@@ -1790,7 +1790,7 @@
         <v>131000</v>
       </c>
       <c r="J33" s="3">
-        <v>119600</v>
+        <v>118600</v>
       </c>
       <c r="K33" s="3">
         <v>-4012800</v>
@@ -1880,7 +1880,7 @@
         <v>131000</v>
       </c>
       <c r="J35" s="3">
-        <v>119600</v>
+        <v>118600</v>
       </c>
       <c r="K35" s="3">
         <v>-4012800</v>
@@ -3650,7 +3650,7 @@
         <v>131000</v>
       </c>
       <c r="J81" s="3">
-        <v>119600</v>
+        <v>118600</v>
       </c>
       <c r="K81" s="3">
         <v>-4012800</v>

--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>PRGO</t>
   </si>
@@ -972,25 +972,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>129000</v>
+        <v>129400</v>
       </c>
       <c r="E14" s="3">
-        <v>96100</v>
+        <v>96500</v>
       </c>
       <c r="F14" s="3">
-        <v>230800</v>
+        <v>144500</v>
       </c>
       <c r="G14" s="3">
-        <v>27600</v>
+        <v>147000</v>
       </c>
       <c r="H14" s="3">
-        <v>55500</v>
+        <v>-49000</v>
       </c>
       <c r="I14" s="3">
-        <v>245900</v>
+        <v>65200</v>
       </c>
       <c r="J14" s="3">
-        <v>244700</v>
+        <v>253600</v>
       </c>
       <c r="K14" s="3">
         <v>2663100</v>
@@ -1017,25 +1017,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>359500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>338600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>312200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>384800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>396500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>423600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>444800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1078,25 +1078,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>4500500</v>
+        <v>4368900</v>
       </c>
       <c r="E17" s="3">
-        <v>4381600</v>
+        <v>4283000</v>
       </c>
       <c r="F17" s="3">
-        <v>3728300</v>
+        <v>3535300</v>
       </c>
       <c r="G17" s="3">
-        <v>3843000</v>
+        <v>3811100</v>
       </c>
       <c r="H17" s="3">
-        <v>3695400</v>
+        <v>3653500</v>
       </c>
       <c r="I17" s="3">
-        <v>4495700</v>
+        <v>4249300</v>
       </c>
       <c r="J17" s="3">
-        <v>4484200</v>
+        <v>4253700</v>
       </c>
       <c r="K17" s="3">
         <v>7281400</v>
@@ -1123,25 +1123,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>155100</v>
+        <v>286700</v>
       </c>
       <c r="E18" s="3">
-        <v>70000</v>
+        <v>168600</v>
       </c>
       <c r="F18" s="3">
-        <v>410400</v>
+        <v>603400</v>
       </c>
       <c r="G18" s="3">
-        <v>245200</v>
+        <v>277100</v>
       </c>
       <c r="H18" s="3">
-        <v>174500</v>
+        <v>216400</v>
       </c>
       <c r="I18" s="3">
-        <v>236000</v>
+        <v>482400</v>
       </c>
       <c r="J18" s="3">
-        <v>462000</v>
+        <v>692500</v>
       </c>
       <c r="K18" s="3">
         <v>-2000800</v>
@@ -1187,25 +1187,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-162800</v>
+        <v>-35600</v>
       </c>
       <c r="E20" s="3">
-        <v>-209100</v>
+        <v>70500</v>
       </c>
       <c r="F20" s="3">
-        <v>-151700</v>
+        <v>80500</v>
       </c>
       <c r="G20" s="3">
-        <v>-239300</v>
+        <v>-6400</v>
       </c>
       <c r="H20" s="3">
-        <v>-26500</v>
+        <v>-8000</v>
       </c>
       <c r="I20" s="3">
-        <v>54600</v>
+        <v>2500</v>
       </c>
       <c r="J20" s="3">
-        <v>-182900</v>
+        <v>-7300</v>
       </c>
       <c r="K20" s="3">
         <v>-2847500</v>
@@ -1232,25 +1232,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>351800</v>
+        <v>681800</v>
       </c>
       <c r="E21" s="3">
-        <v>199500</v>
+        <v>436700</v>
       </c>
       <c r="F21" s="3">
-        <v>570900</v>
+        <v>835100</v>
       </c>
       <c r="G21" s="3">
-        <v>390700</v>
+        <v>668300</v>
       </c>
       <c r="H21" s="3">
-        <v>544500</v>
+        <v>620900</v>
       </c>
       <c r="I21" s="3">
-        <v>714200</v>
+        <v>903500</v>
       </c>
       <c r="J21" s="3">
-        <v>723900</v>
+        <v>1144600</v>
       </c>
       <c r="K21" s="3">
         <v>-4391300</v>
@@ -1277,25 +1277,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>600</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>17</v>
+        <v>201200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>140700</v>
+      </c>
+      <c r="F22" s="3">
+        <v>119700</v>
+      </c>
+      <c r="G22" s="3">
+        <v>130600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>125400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>124100</v>
+      </c>
+      <c r="J22" s="3">
+        <v>166100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>17</v>
@@ -1340,7 +1340,7 @@
         <v>290600</v>
       </c>
       <c r="J23" s="3">
-        <v>279100</v>
+        <v>280100</v>
       </c>
       <c r="K23" s="3">
         <v>-4848300</v>
@@ -1385,7 +1385,7 @@
         <v>159600</v>
       </c>
       <c r="J24" s="3">
-        <v>145400</v>
+        <v>160500</v>
       </c>
       <c r="K24" s="3">
         <v>-835500</v>
@@ -1475,7 +1475,7 @@
         <v>131000</v>
       </c>
       <c r="J26" s="3">
-        <v>133700</v>
+        <v>119600</v>
       </c>
       <c r="K26" s="3">
         <v>-4012800</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-4400</v>
+        <v>-12700</v>
       </c>
       <c r="E27" s="3">
-        <v>-130900</v>
+        <v>-140600</v>
       </c>
       <c r="F27" s="3">
-        <v>-130900</v>
+        <v>-68900</v>
       </c>
       <c r="G27" s="3">
-        <v>44200</v>
+        <v>-162600</v>
       </c>
       <c r="H27" s="3">
-        <v>158700</v>
+        <v>146100</v>
       </c>
       <c r="I27" s="3">
         <v>131000</v>
       </c>
       <c r="J27" s="3">
-        <v>133700</v>
+        <v>119600</v>
       </c>
       <c r="K27" s="3">
         <v>-4012800</v>
@@ -1606,11 +1606,11 @@
       <c r="H29" s="3">
         <v>-12600</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>17</v>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-15100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>17</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>162800</v>
+        <v>35600</v>
       </c>
       <c r="E32" s="3">
-        <v>209100</v>
+        <v>-70500</v>
       </c>
       <c r="F32" s="3">
-        <v>151700</v>
+        <v>-80500</v>
       </c>
       <c r="G32" s="3">
-        <v>239300</v>
+        <v>6400</v>
       </c>
       <c r="H32" s="3">
-        <v>26500</v>
+        <v>8000</v>
       </c>
       <c r="I32" s="3">
-        <v>-54600</v>
+        <v>-2500</v>
       </c>
       <c r="J32" s="3">
-        <v>182900</v>
+        <v>7300</v>
       </c>
       <c r="K32" s="3">
         <v>2847500</v>
@@ -1790,7 +1790,7 @@
         <v>131000</v>
       </c>
       <c r="J33" s="3">
-        <v>118600</v>
+        <v>119600</v>
       </c>
       <c r="K33" s="3">
         <v>-4012800</v>
@@ -1880,7 +1880,7 @@
         <v>131000</v>
       </c>
       <c r="J35" s="3">
-        <v>118600</v>
+        <v>119600</v>
       </c>
       <c r="K35" s="3">
         <v>-4012800</v>
@@ -1995,7 +1995,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>751300</v>
+        <v>744300</v>
       </c>
       <c r="E41" s="3">
         <v>600700</v>
@@ -2004,7 +2004,7 @@
         <v>1864900</v>
       </c>
       <c r="G41" s="3">
-        <v>641500</v>
+        <v>631500</v>
       </c>
       <c r="H41" s="3">
         <v>354300</v>
@@ -2043,7 +2043,7 @@
         <v>100</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>3100</v>
       </c>
       <c r="F42" s="3">
         <v>400</v>
@@ -2054,11 +2054,11 @@
       <c r="H42" s="3">
         <v>6600</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>17</v>
+      <c r="I42" s="3">
+        <v>9400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>17000</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>17</v>
@@ -2094,16 +2094,16 @@
         <v>693100</v>
       </c>
       <c r="G43" s="3">
-        <v>1073900</v>
+        <v>613200</v>
       </c>
       <c r="H43" s="3">
         <v>1269500</v>
       </c>
       <c r="I43" s="3">
-        <v>1073100</v>
+        <v>1098600</v>
       </c>
       <c r="J43" s="3">
-        <v>1130800</v>
+        <v>1151300</v>
       </c>
       <c r="K43" s="3">
         <v>1176000</v>
@@ -2139,7 +2139,7 @@
         <v>1020200</v>
       </c>
       <c r="G44" s="3">
-        <v>1200200</v>
+        <v>1059400</v>
       </c>
       <c r="H44" s="3">
         <v>967300</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>172500</v>
+        <v>28900</v>
       </c>
       <c r="E45" s="3">
-        <v>230200</v>
+        <v>3500</v>
       </c>
       <c r="F45" s="3">
-        <v>281300</v>
+        <v>25500</v>
       </c>
       <c r="G45" s="3">
-        <v>215400</v>
+        <v>676200</v>
       </c>
       <c r="H45" s="3">
-        <v>159200</v>
+        <v>4300</v>
       </c>
       <c r="I45" s="3">
-        <v>400000</v>
+        <v>3800</v>
       </c>
       <c r="J45" s="3">
-        <v>203200</v>
+        <v>6300</v>
       </c>
       <c r="K45" s="3">
         <v>212000</v>
@@ -2232,7 +2232,7 @@
         <v>3133500</v>
       </c>
       <c r="H46" s="3">
-        <v>2756900</v>
+        <v>2730600</v>
       </c>
       <c r="I46" s="3">
         <v>2902200</v>
@@ -2265,13 +2265,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>60100</v>
+        <v>91900</v>
       </c>
       <c r="E47" s="3">
-        <v>63400</v>
+        <v>112600</v>
       </c>
       <c r="F47" s="3">
-        <v>66400</v>
+        <v>68200</v>
       </c>
       <c r="G47" s="3">
         <v>71700</v>
@@ -2279,11 +2279,11 @@
       <c r="H47" s="3">
         <v>20100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
+      <c r="I47" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J47" s="3">
+        <v>11200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>17</v>
@@ -2319,7 +2319,7 @@
         <v>1058900</v>
       </c>
       <c r="G48" s="3">
-        <v>1213000</v>
+        <v>1049100</v>
       </c>
       <c r="H48" s="3">
         <v>1060300</v>
@@ -2364,7 +2364,7 @@
         <v>5150800</v>
       </c>
       <c r="G49" s="3">
-        <v>6758200</v>
+        <v>5584200</v>
       </c>
       <c r="H49" s="3">
         <v>7106700</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>287200</v>
+        <v>229600</v>
       </c>
       <c r="E52" s="3">
-        <v>289400</v>
+        <v>233100</v>
       </c>
       <c r="F52" s="3">
-        <v>289700</v>
+        <v>281400</v>
       </c>
       <c r="G52" s="3">
-        <v>312000</v>
+        <v>1609300</v>
       </c>
       <c r="H52" s="3">
-        <v>357400</v>
+        <v>378300</v>
       </c>
       <c r="I52" s="3">
-        <v>364100</v>
+        <v>343400</v>
       </c>
       <c r="J52" s="3">
-        <v>419900</v>
+        <v>398300</v>
       </c>
       <c r="K52" s="3">
         <v>284000</v>
@@ -2672,7 +2672,7 @@
         <v>411200</v>
       </c>
       <c r="G57" s="3">
-        <v>543800</v>
+        <v>451600</v>
       </c>
       <c r="H57" s="3">
         <v>520200</v>
@@ -2708,19 +2708,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>440600</v>
+        <v>468100</v>
       </c>
       <c r="E58" s="3">
-        <v>36200</v>
+        <v>64600</v>
       </c>
       <c r="F58" s="3">
-        <v>603800</v>
+        <v>629800</v>
       </c>
       <c r="G58" s="3">
-        <v>37800</v>
+        <v>65600</v>
       </c>
       <c r="H58" s="3">
-        <v>3400</v>
+        <v>35400</v>
       </c>
       <c r="I58" s="3">
         <v>190200</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>668000</v>
+        <v>186800</v>
       </c>
       <c r="E59" s="3">
-        <v>540100</v>
+        <v>87000</v>
       </c>
       <c r="F59" s="3">
-        <v>572900</v>
+        <v>65600</v>
       </c>
       <c r="G59" s="3">
-        <v>800400</v>
+        <v>436500</v>
       </c>
       <c r="H59" s="3">
-        <v>812200</v>
+        <v>40600</v>
       </c>
       <c r="I59" s="3">
-        <v>872300</v>
+        <v>105700</v>
       </c>
       <c r="J59" s="3">
-        <v>915400</v>
+        <v>119900</v>
       </c>
       <c r="K59" s="3">
         <v>791800</v>
@@ -2843,19 +2843,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3632800</v>
+        <v>3804100</v>
       </c>
       <c r="E61" s="3">
-        <v>4070400</v>
+        <v>4259900</v>
       </c>
       <c r="F61" s="3">
-        <v>2916700</v>
+        <v>3064000</v>
       </c>
       <c r="G61" s="3">
-        <v>3528300</v>
+        <v>3660100</v>
       </c>
       <c r="H61" s="3">
-        <v>3365800</v>
+        <v>3467500</v>
       </c>
       <c r="I61" s="3">
         <v>3052200</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>822100</v>
+        <v>360000</v>
       </c>
       <c r="E62" s="3">
-        <v>991200</v>
+        <v>408200</v>
       </c>
       <c r="F62" s="3">
-        <v>769400</v>
+        <v>343700</v>
       </c>
       <c r="G62" s="3">
-        <v>923000</v>
+        <v>471900</v>
       </c>
       <c r="H62" s="3">
-        <v>795700</v>
+        <v>376100</v>
       </c>
       <c r="I62" s="3">
-        <v>725700</v>
+        <v>411000</v>
       </c>
       <c r="J62" s="3">
-        <v>751400</v>
+        <v>396000</v>
       </c>
       <c r="K62" s="3">
         <v>851700</v>
@@ -3080,13 +3080,13 @@
         <v>5833300</v>
       </c>
       <c r="H66" s="3">
-        <v>5497600</v>
+        <v>5497300</v>
       </c>
       <c r="I66" s="3">
-        <v>5315400</v>
+        <v>5315300</v>
       </c>
       <c r="J66" s="3">
-        <v>5458300</v>
+        <v>5458200</v>
       </c>
       <c r="K66" s="3">
         <v>7912000</v>
@@ -3650,7 +3650,7 @@
         <v>131000</v>
       </c>
       <c r="J81" s="3">
-        <v>118600</v>
+        <v>119600</v>
       </c>
       <c r="K81" s="3">
         <v>-4012800</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>359500</v>
+        <v>93700</v>
       </c>
       <c r="E83" s="3">
-        <v>338600</v>
+        <v>86200</v>
       </c>
       <c r="F83" s="3">
-        <v>312200</v>
+        <v>102200</v>
       </c>
       <c r="G83" s="3">
-        <v>384800</v>
+        <v>172600</v>
       </c>
       <c r="H83" s="3">
-        <v>396500</v>
+        <v>176900</v>
       </c>
       <c r="I83" s="3">
-        <v>423600</v>
+        <v>90000</v>
       </c>
       <c r="J83" s="3">
-        <v>444800</v>
+        <v>95200</v>
       </c>
       <c r="K83" s="3">
         <v>457000</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-149700</v>
+        <v>149700</v>
       </c>
       <c r="E96" s="3">
-        <v>-142400</v>
+        <v>142400</v>
       </c>
       <c r="F96" s="3">
-        <v>-129600</v>
+        <v>129600</v>
       </c>
       <c r="G96" s="3">
-        <v>-123900</v>
+        <v>123900</v>
       </c>
       <c r="H96" s="3">
-        <v>-112400</v>
+        <v>112400</v>
       </c>
       <c r="I96" s="3">
-        <v>-104900</v>
+        <v>104900</v>
       </c>
       <c r="J96" s="3">
-        <v>-91100</v>
+        <v>91100</v>
       </c>
       <c r="K96" s="3">
         <v>-83200</v>

--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42182</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41818</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41454</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41090</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4373400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4655600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4451600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4138700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4088200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3869900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4731700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4946200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5280600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2632200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4603900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4060800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3539800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3173200</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2830700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2975200</v>
       </c>
-      <c r="E9" s="3">
-        <v>2996200</v>
-      </c>
       <c r="F9" s="3">
+        <v>2972400</v>
+      </c>
+      <c r="G9" s="3">
         <v>2722500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2593300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2436200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2900200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2966700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3228800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1553300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2891400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2613100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2259800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2077700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1542700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1680400</v>
       </c>
-      <c r="E10" s="3">
-        <v>1455400</v>
-      </c>
       <c r="F10" s="3">
+        <v>1479200</v>
+      </c>
+      <c r="G10" s="3">
         <v>1416200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1494900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1433700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1831500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1979500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2051800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1078900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1712500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1447700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1280000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1095600</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,53 +888,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>112200</v>
+      </c>
+      <c r="E12" s="3">
         <v>122500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>123100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>122000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>121700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>119200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>218600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>167700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>184000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>88200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>187800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>152500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>115200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>105800</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -965,81 +981,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>300400</v>
+      </c>
+      <c r="E14" s="3">
         <v>129400</v>
       </c>
-      <c r="E14" s="3">
-        <v>96500</v>
-      </c>
       <c r="F14" s="3">
+        <v>120300</v>
+      </c>
+      <c r="G14" s="3">
         <v>144500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>147000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-49000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>65200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>253600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2663100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>243400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>218800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>325900</v>
+      </c>
+      <c r="E15" s="3">
         <v>359500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>338600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>312200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>384800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>396500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>423600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>444800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1055,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>4368900</v>
+        <v>3956100</v>
       </c>
       <c r="E17" s="3">
-        <v>4283000</v>
+        <v>4366600</v>
       </c>
       <c r="F17" s="3">
+        <v>4258700</v>
+      </c>
+      <c r="G17" s="3">
         <v>3535300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3811100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3653500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4249300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4253700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7281400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2565500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3866700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3659600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2860700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2604000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>286700</v>
+        <v>417300</v>
       </c>
       <c r="E18" s="3">
-        <v>168600</v>
+        <v>289000</v>
       </c>
       <c r="F18" s="3">
+        <v>192900</v>
+      </c>
+      <c r="G18" s="3">
         <v>603400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>277100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>216400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>482400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>692500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2000800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>66700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>737200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>401200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>679100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>569200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-35600</v>
+        <v>-19100</v>
       </c>
       <c r="E20" s="3">
-        <v>70500</v>
+        <v>-33300</v>
       </c>
       <c r="F20" s="3">
+        <v>71000</v>
+      </c>
+      <c r="G20" s="3">
         <v>80500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2847500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>31100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-342100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>762300</v>
+      </c>
+      <c r="E21" s="3">
         <v>681800</v>
       </c>
-      <c r="E21" s="3">
-        <v>436700</v>
-      </c>
       <c r="F21" s="3">
+        <v>460500</v>
+      </c>
+      <c r="G21" s="3">
         <v>835100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>668300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>620900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>903500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1144600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4391300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>280200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>943900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>737100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>837900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>712000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>216700</v>
+      </c>
+      <c r="E22" s="3">
         <v>201200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>140700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>119700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>130600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>125400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>124100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>166100</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>88900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>147100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>105600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>70000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>64700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-80700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-8300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-139100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>258700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>148000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>290600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>280100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4848300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>248000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>272600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>607700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>512000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>389600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-38300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>159600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>160500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-835500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-33600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>120000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>67300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>165800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>119000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-160700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-130900</v>
       </c>
       <c r="F26" s="3">
         <v>-130900</v>
       </c>
       <c r="G26" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="H26" s="3">
         <v>44200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>158700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>131000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>119600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4012800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>42500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>128000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>205300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>441900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>393000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-140600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-68900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-162600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>146100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>131000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>119600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4012800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>42500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>128000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>205300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>441900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>393000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,35 +1642,38 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-8300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-9700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>62000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-206800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-12600</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>17</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>17</v>
@@ -1621,18 +1681,21 @@
       <c r="M29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>8600</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>35600</v>
+        <v>19100</v>
       </c>
       <c r="E32" s="3">
-        <v>-70500</v>
+        <v>33300</v>
       </c>
       <c r="F32" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-80500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2847500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-31100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>342100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-140600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-68900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-162600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>146100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>131000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>119600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4012800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>42500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>128000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>205300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>441900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>401600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-140600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-68900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-162600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>146100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>131000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>119600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4012800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>42500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>128000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>205300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>441900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>401600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42182</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41818</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41454</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41090</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,413 +2074,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>558800</v>
+      </c>
+      <c r="E41" s="3">
         <v>744300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>600700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1864900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>631500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>354300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>551100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>678700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>622300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>417800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>785600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>799500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1559800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>602500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>9400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17000</v>
       </c>
-      <c r="K42" s="3" t="s">
+      <c r="L42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>800</v>
       </c>
-      <c r="P42" s="3" t="s">
+      <c r="Q42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>686200</v>
+      </c>
+      <c r="E43" s="3">
         <v>768100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>738600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>693100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>613200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1269500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1098600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1151300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1176000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2710900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1282100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>935100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1316000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>573600</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1081800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1140900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1150300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1020200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1059400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>967300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>878000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>806900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>795000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>898700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>838900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>631600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1407800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>547500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28900</v>
+        <v>9600</v>
       </c>
       <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>3500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>676200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>212000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>286100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>263600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>178800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>195500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>72300</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2481900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2832900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2719900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3859900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3133500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2730600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2902200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2819600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2805300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2791600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3182900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2550900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2236900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1795900</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E47" s="3">
         <v>91900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>112600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>68200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>71700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>19500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11200</v>
       </c>
-      <c r="K47" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>220500</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" s="3">
         <v>4400</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1104700</v>
+      </c>
+      <c r="E48" s="3">
         <v>1113700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1165400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1058900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1049100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1060300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>829100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>833100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>870100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1772400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>932400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>779900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2653200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>578400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5749100</v>
+      </c>
+      <c r="E49" s="3">
         <v>6515200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6779200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5150800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5584200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7106700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>6888000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7556200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9910700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15352100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15340600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10330800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4663400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1549400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>239500</v>
+      </c>
+      <c r="E52" s="3">
         <v>229600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>233100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>281400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1609300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>378300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>343400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>398300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>284000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>336200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>264700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>191200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>201600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>100400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9647700</v>
+      </c>
+      <c r="E54" s="3">
         <v>10809100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11017300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10425700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11488400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11301400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10983400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11628800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13870100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19349600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19720600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13852800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5350800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4024000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>495200</v>
+      </c>
+      <c r="E57" s="3">
         <v>477700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>537300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>411200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>451600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>520200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>474900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>450200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>471700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1468900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>747500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>364300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>764000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>317300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E58" s="3">
         <v>468100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>629800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>65600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>35400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>190200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>70400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>572800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7050400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>64600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>143700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>92400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>40100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E59" s="3">
         <v>186800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>87000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>65600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>436500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>105700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>119900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>791800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1172600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>881600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>566700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>642400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>295300</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1044200</v>
+      </c>
+      <c r="E60" s="3">
         <v>1586300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1113600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1587900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1382000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1335800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1537400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1436000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1836300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2552200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1693700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1074700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>749400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>652700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3758100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3804100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4259900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3064000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3660100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3467500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3052200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3270800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5224500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4971600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5246900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3063100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1927800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1329200</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>360000</v>
+        <v>295400</v>
       </c>
       <c r="E62" s="3">
+        <v>358200</v>
+      </c>
+      <c r="F62" s="3">
         <v>408200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>343700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>471900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>376100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>411000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>396000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>851700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3341800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2117200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1021300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>682000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>189400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5328300</v>
+      </c>
+      <c r="E66" s="3">
         <v>6041200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6175200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5274000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5833300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5497300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5315300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5458200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7912000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9242200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9058000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5159900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3019400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2173000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2252100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2080300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2067600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1927000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1858100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1695500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1838300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1975500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2095100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3462100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1938300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1875100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3431800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1306900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4319400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4767900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4842100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5151700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5655100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5803800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5668000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6170500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5958100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10107400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10662600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8692900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2331400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1851000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42182</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41818</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41454</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41090</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-140600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-68900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-162600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>146100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>131000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>119600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4012800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>42500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>128000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>205300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>441900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>401600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>97400</v>
+      </c>
+      <c r="E83" s="3">
         <v>93700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>86200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>102200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>172600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>176900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>90000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>95200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>457000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>182400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>548800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>358900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>160200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>135300</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>362900</v>
+      </c>
+      <c r="E89" s="3">
         <v>405500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>307300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>156300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>636200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>387800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>593000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>698900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>654900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>200900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1198300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>693500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>553800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>513400</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-131600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-101700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-96400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-222700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-205600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-286800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-138200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-88600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-171300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-77800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-137000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-171600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-104100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-120900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-77500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1958600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1275800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-187800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-596100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-126800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2338100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-175000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-708100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2646900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1704800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-947800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-684100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>152500</v>
+      </c>
+      <c r="E96" s="3">
         <v>149700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>142400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>129600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>123900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>112400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>104900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>91100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-83200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-36300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-64800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-46100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-33000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-29000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-611000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-187200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>421600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-178700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-181100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-571900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3004700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-268700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>149600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1523900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1028000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>577200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>458700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="E101" s="3">
         <v>9800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-48900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-15600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>19900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-21900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>24100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-6700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-89200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-192500</v>
+      </c>
+      <c r="E102" s="3">
         <v>150600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1278600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1237800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>287200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-196800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-127600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>56400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>204500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-367800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>177400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>292400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42182</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41818</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41454</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41090</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4253100</v>
+      </c>
+      <c r="E8" s="3">
         <v>4373400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4655600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4451600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4138700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4088200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3869900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4731700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4946200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5280600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2632200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4603900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4060800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3539800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3173200</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2758600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2830700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2975200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2972400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2722500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2593300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2436200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2900200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2966700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3228800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1553300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2891400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2613100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2259800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2077700</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1494500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1542700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1680400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1479200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1416200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1494900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1433700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1831500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1979500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2051800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1078900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1712500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1447700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1280000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1095600</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,56 +901,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>95400</v>
+      </c>
+      <c r="E12" s="3">
         <v>112200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>122500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>123100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>122000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>121700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>119200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>218600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>167700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>184000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>88200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>187800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>152500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>115200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>105800</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -984,87 +1000,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>300400</v>
+        <v>1499000</v>
       </c>
       <c r="E14" s="3">
+        <v>204400</v>
+      </c>
+      <c r="F14" s="3">
         <v>129400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>120300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>144500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>147000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-49000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>65200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>253600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2663100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>243400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>15600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>218800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>8800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>337500</v>
+      </c>
+      <c r="E15" s="3">
         <v>325900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>359500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>338600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>312200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>384800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>396500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>423600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>444800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3956100</v>
+        <v>3877300</v>
       </c>
       <c r="E17" s="3">
-        <v>4366600</v>
+        <v>4052100</v>
       </c>
       <c r="F17" s="3">
+        <v>4367000</v>
+      </c>
+      <c r="G17" s="3">
         <v>4258700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3535300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3811100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3653500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4249300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4253700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7281400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2565500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3866700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3659600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2860700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2604000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>417300</v>
+        <v>375800</v>
       </c>
       <c r="E18" s="3">
-        <v>289000</v>
+        <v>321300</v>
       </c>
       <c r="F18" s="3">
+        <v>288600</v>
+      </c>
+      <c r="G18" s="3">
         <v>192900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>603400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>277100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>216400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>482400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>692500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2000800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>66700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>737200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>401200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>679100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>569200</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-25700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-33300</v>
-      </c>
       <c r="F20" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="G20" s="3">
         <v>71000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>80500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-6400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2847500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>31100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-342100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-23000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>762300</v>
+        <v>739000</v>
       </c>
       <c r="E21" s="3">
+        <v>666300</v>
+      </c>
+      <c r="F21" s="3">
         <v>681800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>460500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>835100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>668300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>620900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>903500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1144600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4391300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>280200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>943900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>737100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>837900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>712000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>200400</v>
+      </c>
+      <c r="E22" s="3">
         <v>216700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>201200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>140700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>119700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>130600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>125400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>124100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>166100</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>88900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>147100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>105600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>70000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>64700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1297900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-80700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-139100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>258700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>148000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>290600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>280100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4848300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>248000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>272600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>607700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>512000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>104400</v>
+      </c>
+      <c r="E24" s="3">
         <v>80000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-8200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>389600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-38300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>159600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>160500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-835500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-33600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>120000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>67300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>119000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1402300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-160700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4400</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-130900</v>
       </c>
       <c r="G26" s="3">
         <v>-130900</v>
       </c>
       <c r="H26" s="3">
+        <v>-130900</v>
+      </c>
+      <c r="I26" s="3">
         <v>44200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>158700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>119600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4012800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>42500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>128000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>205300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>441900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>393000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1425400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-171800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-140600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-68900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-162600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>146100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>131000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>119600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4012800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>42500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>128000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>205300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>441900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>393000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,38 +1702,41 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-11100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-8300</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-9700</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>62000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-206800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-12600</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>17</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>17</v>
@@ -1684,18 +1744,21 @@
       <c r="N29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>8600</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E32" s="3">
         <v>19100</v>
       </c>
-      <c r="E32" s="3">
-        <v>33300</v>
-      </c>
       <c r="F32" s="3">
+        <v>33700</v>
+      </c>
+      <c r="G32" s="3">
         <v>-71000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-80500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>6400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2847500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-31100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>342100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>23000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1425400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-171800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-140600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-68900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-162600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>146100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>131000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>119600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4012800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>42500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>128000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>205300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>441900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>401600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1425400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-171800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-140600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-68900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-162600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>146100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>131000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>119600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4012800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>42500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>128000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>205300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>441900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>401600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42182</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41818</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41454</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41090</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>531600</v>
+      </c>
+      <c r="E41" s="3">
         <v>558800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>744300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>600700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1864900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>631500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>354300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>551100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>678700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>622300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>417800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>785600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>799500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1559800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>602500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2132,383 +2221,407 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>17000</v>
       </c>
-      <c r="L42" s="3" t="s">
+      <c r="M42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>12700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>800</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="R42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>650100</v>
+      </c>
+      <c r="E43" s="3">
         <v>686200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>768100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>738600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>693100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>613200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1269500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1098600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1151300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1176000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2710900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1282100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>935100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1316000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>573600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1149000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1081800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1140900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1150300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1020200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1059400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>967300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>878000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>806900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>795000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>898700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>838900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>631600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1407800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>547500</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9600</v>
+        <v>301900</v>
       </c>
       <c r="E45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>676200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>212000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>286100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>263600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>178800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>195500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>72300</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2797400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2481900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2832900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2719900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3859900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3133500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2730600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2902200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2819600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2805300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2791600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3182900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2550900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2236900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1795900</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E47" s="3">
         <v>67400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>91900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>112600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>68200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>71700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>19500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11200</v>
       </c>
-      <c r="L47" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>220500</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q47" s="3">
         <v>4400</v>
       </c>
-      <c r="Q47" s="3" t="s">
+      <c r="R47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1104700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1113700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1165400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1058900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1049100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1060300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>829100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>833100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>870100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1772400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>932400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>779900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2653200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>578400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4406200</v>
+      </c>
+      <c r="E49" s="3">
         <v>5749100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6515200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6779200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5150800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5584200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7106700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>6888000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7556200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9910700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15352100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15340600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10330800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4663400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1549400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>224900</v>
+      </c>
+      <c r="E52" s="3">
         <v>239500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>229600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>233100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>281400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1609300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>378300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>343400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>398300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>284000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>336200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>264700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>191200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>201600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>100400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8535200</v>
+      </c>
+      <c r="E54" s="3">
         <v>9647700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10809100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11017300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10425700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11488400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11301400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10983400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11628800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13870100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19349600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19720600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>13852800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5350800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4024000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>474500</v>
+      </c>
+      <c r="E57" s="3">
         <v>495200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>477700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>537300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>411200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>451600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>520200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>474900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>450200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>471700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1468900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>747500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>364300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>764000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>317300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>62300</v>
+      </c>
+      <c r="E58" s="3">
         <v>64200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>468100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>629800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>65600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>35400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>190200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>70400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>572800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7050400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>64600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>143700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>92400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>40100</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E59" s="3">
         <v>99800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>186800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>87000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>65600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>436500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>105700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>119900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>791800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1172600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>881600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>566700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>642400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>295300</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1012900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1044200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1586300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1113600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1587900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1382000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1335800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1537400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1436000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1836300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2552200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1693700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1074700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>749400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>652700</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3787900</v>
+      </c>
+      <c r="E61" s="3">
         <v>3758100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3804100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4259900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3064000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3660100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3467500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3052200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3270800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5224500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4971600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5246900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3063100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1927800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1329200</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>602600</v>
+      </c>
+      <c r="E62" s="3">
         <v>295400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>358200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>408200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>343700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>471900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>376100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>411000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>396000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>851700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3341800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2117200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1021300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>682000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>189400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5599700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5328300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6041200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6175200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5274000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5833300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5497300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5315300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5458200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7912000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9242200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9058000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5159900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3019400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2173000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3677500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2252100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2080300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2067600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1927000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1858100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1695500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1838300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1975500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2095100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3462100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1938300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1875100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3431800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1306900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2935500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4319400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4767900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4842100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5151700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5655100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5803800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5668000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6170500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5958100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10107400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10662600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8692900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2331400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1851000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42182</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41818</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41454</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41090</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1425400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-171800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-140600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-68900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-162600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>146100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>131000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>119600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4012800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>42500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>128000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>205300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>441900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>401600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E83" s="3">
         <v>97400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>93700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>86200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>102200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>172600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>176900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>95200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>457000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>182400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>548800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>358900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>160200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>135300</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>238500</v>
+      </c>
+      <c r="E89" s="3">
         <v>362900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>405500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>307300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>156300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>636200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>387800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>593000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>698900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>654900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1198300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>693500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>553800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>513400</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-94900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-131600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-101700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-96400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-222700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-205600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-286800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-138200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-171300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-77800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-137000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-171600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-104100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-120900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="E94" s="3">
         <v>78800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-77500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1958600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1275800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-187800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-596100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-126800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2338100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-175000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-708100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2646900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1704800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-947800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-684100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>159300</v>
+      </c>
+      <c r="E96" s="3">
         <v>152500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>149700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>142400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>129600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>123900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>112400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>104900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>91100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-83200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-36300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-64800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-46100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-33000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-29000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-220500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-611000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-187200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>421600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-178700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-181100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-571900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3004700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-268700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>149600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1523900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1028000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>577200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>458700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-23200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-48900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-15600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>19900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-21900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>24100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-6700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-89200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4400</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-192500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>150600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1278600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1237800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>287200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-196800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-127600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>56400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>204500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-367800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>177400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>292400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRGO_YR_FIN.xlsx
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1499000</v>
+        <v>1465400</v>
       </c>
       <c r="E14" s="3">
         <v>204400</v>
@@ -1130,7 +1130,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3877300</v>
+        <v>3910900</v>
       </c>
       <c r="E17" s="3">
         <v>4052100</v>
@@ -1181,7 +1181,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>375800</v>
+        <v>342200</v>
       </c>
       <c r="E18" s="3">
         <v>321300</v>
@@ -1304,7 +1304,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>739000</v>
+        <v>705400</v>
       </c>
       <c r="E21" s="3">
         <v>666300</v>
